--- a/astro-site/public/dl/kit-tareas-chef-privado/03-equipo-transporte.xlsx
+++ b/astro-site/public/dl/kit-tareas-chef-privado/03-equipo-transporte.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Equipo Transporte" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo Transporte" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Equipo Transporte'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +81,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -143,54 +150,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -550,15 +568,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -566,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -594,9 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -618,8 +636,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chef-privado · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -628,18 +663,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -852,6 +888,7 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -991,6 +1028,7 @@
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="13" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -1130,6 +1168,7 @@
       <c r="F29" s="11" t="n"/>
       <c r="G29" s="13" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -1326,6 +1365,7 @@
       <c r="F40" s="11" t="n"/>
       <c r="G40" s="13" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
@@ -1465,6 +1505,7 @@
       <c r="F48" s="11" t="n"/>
       <c r="G48" s="13" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
@@ -1603,6 +1644,26 @@
       <c r="E56" s="12" t="n"/>
       <c r="F56" s="11" t="n"/>
       <c r="G56" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C57">
+        <f>COUNTIF(E6:E56,"✓")</f>
+        <v>5.0</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E57">
+        <f>COUNTIF(B6:B56,"?*")</f>
+        <v>41.0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -1631,11 +1692,25 @@
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A42:G42"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G56">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E25 E26 E27 E28 E29 E33 E34 E35 E36 E37 E38 E39 E40 E44 E45 E46 E47 E48 E52 E53 E54 E55 E56" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E25 E26 E27 E28 E29 E33 E34 E35 E36 E37 E38 E39 E40 E44 E45 E46 E47 E48 E52 E53 E54 E55 E56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>